--- a/Bai1.3_TestCase.xlsx
+++ b/Bai1.3_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Software-Testing\Buoi7\1150080143_VoAnhKiet_CNPM2_Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E33529-325D-4B42-9B65-169FC71A3C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD00007-5930-444D-ADFD-9CCBBC0DE579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,9 +116,6 @@
     <t>Các bước thực hiện</t>
   </si>
   <si>
-    <t>KIỂM THỬ LOGIC ĐĂNG KÝ</t>
-  </si>
-  <si>
     <t>Logic xử lý dự kiến:</t>
   </si>
   <si>
@@ -443,6 +440,9 @@
   <si>
     <t>B1: Nhận Webhook trả về từ Cổng thanh toán (Success).
 B2: Verify chữ ký và cập nhật trạng thái.</t>
+  </si>
+  <si>
+    <t>KIỂM THỬ</t>
   </si>
 </sst>
 </file>
@@ -652,26 +652,26 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -972,14 +972,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="A1" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
@@ -996,16 +996,16 @@
         <v>20</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="D3" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -1091,18 +1091,18 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" ht="78" x14ac:dyDescent="0.3">
-      <c r="A9" s="29">
+      <c r="A9" s="27">
         <v>1</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>37</v>
+      <c r="B9" s="27" t="s">
+        <v>36</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="29">
+      <c r="D9" s="27">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -1110,18 +1110,18 @@
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="29">
+      <c r="A10" s="27">
         <v>2</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>38</v>
+      <c r="B10" s="27" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="29">
+      <c r="D10" s="27">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -1129,18 +1129,18 @@
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="29">
+      <c r="A11" s="27">
         <v>3</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>39</v>
+      <c r="B11" s="27" t="s">
+        <v>38</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="29">
+      <c r="D11" s="27">
         <v>3</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -1161,7 +1161,7 @@
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1174,7 +1174,7 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1187,7 +1187,7 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1200,7 +1200,7 @@
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -1213,7 +1213,7 @@
     <row r="17" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -1224,7 +1224,7 @@
     <row r="18" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -1261,15 +1261,15 @@
         <v>3</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1284,36 +1284,36 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="C27" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="28" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="28" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="C28" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="5" t="s">
+    </row>
+    <row r="29" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="27" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="29" t="s">
+      <c r="B29" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="C29" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -1325,50 +1325,50 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26" t="s">
+    <row r="32" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="C32" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="27" t="s">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="27" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="29" t="s">
+      <c r="B33" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="C33" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="29" t="s">
+      <c r="B34" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="C34" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="D34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="29" t="s">
+      <c r="B35" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="C35" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="D35" s="1"/>
     </row>
@@ -1401,292 +1401,292 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="C40" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="D40" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="29" t="s">
+    </row>
+    <row r="41" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="E40" s="29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="29" t="s">
+      <c r="E41" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="E41" s="5" t="s">
+    </row>
+    <row r="42" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="27" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="29" t="s">
+      <c r="B42" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="C42" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="29" t="s">
+      <c r="E42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E42" s="5" t="s">
+    </row>
+    <row r="43" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="27" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="29" t="s">
+      <c r="B43" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="C43" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" s="29" t="s">
+      <c r="E43" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="5" t="s">
+    </row>
+    <row r="44" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="27" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="29" t="s">
+      <c r="B44" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="C44" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="29" t="s">
+      <c r="E44" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="5" t="s">
+    </row>
+    <row r="45" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="27" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="29" t="s">
+      <c r="B45" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="C45" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C45" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="29" t="s">
+      <c r="E45" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="5" t="s">
+    </row>
+    <row r="46" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="27" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="29" t="s">
+      <c r="B46" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="C46" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="29" t="s">
+      <c r="E46" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="5" t="s">
+    </row>
+    <row r="47" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="27" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="29" t="s">
+      <c r="B47" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="C47" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="29" t="s">
+      <c r="E47" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E47" s="5" t="s">
+    </row>
+    <row r="48" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="29" t="s">
+      <c r="B48" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B48" s="29" t="s">
+      <c r="C48" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D48" s="29" t="s">
+      <c r="E48" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="5" t="s">
+    </row>
+    <row r="49" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="27" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="29" t="s">
+      <c r="B49" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="C49" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="29" t="s">
+      <c r="E49" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E49" s="5" t="s">
+    </row>
+    <row r="50" spans="1:5" s="12" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="27" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" s="12" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="29" t="s">
+      <c r="B50" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="C50" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C50" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="29" t="s">
+      <c r="E50" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E50" s="5" t="s">
+    </row>
+    <row r="51" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="27" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="29" t="s">
+      <c r="B51" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="C51" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="29" t="s">
+      <c r="E51" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E51" s="5" t="s">
+    </row>
+    <row r="52" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="27" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="29" t="s">
+      <c r="B52" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="C52" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="D52" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="29" t="s">
+      <c r="E52" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E52" s="5" t="s">
+    </row>
+    <row r="53" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="27" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="29" t="s">
+      <c r="B53" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="C53" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="C53" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" s="29" t="s">
+      <c r="E53" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E53" s="5" t="s">
+    </row>
+    <row r="54" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="27" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="29" t="s">
+      <c r="B54" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="C54" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" s="29" t="s">
+      <c r="E54" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="5" t="s">
+    </row>
+    <row r="55" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="27" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="29" t="s">
+      <c r="B55" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="C55" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D55" s="29" t="s">
+      <c r="E55" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E55" s="5" t="s">
+    </row>
+    <row r="56" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="27" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" s="12" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="29" t="s">
+      <c r="B56" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="C56" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" s="29" t="s">
+      <c r="E56" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
